--- a/APM_2.0_graphs_and_data/APM_3.5_Summary.xlsx
+++ b/APM_2.0_graphs_and_data/APM_3.5_Summary.xlsx
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -130,9 +130,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1722,31 +1719,31 @@
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="6" t="n">
+      <c r="A58" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>5×5</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>2/100</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>80003686400</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>2.00%</t>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>7×7</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>100/100</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>3655139651328</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
